--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487887_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487887_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8038</v>
+        <v>2.3935</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0033</v>
+        <v>0.2113</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8005</v>
+        <v>2.1822</v>
       </c>
       <c r="G2" t="n">
         <v>1.7636</v>
@@ -610,13 +610,13 @@
         <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6427</v>
+        <v>1.2324</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5683</v>
+        <v>0.7763</v>
       </c>
       <c r="U2" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.4561</v>
       </c>
       <c r="V2" t="n">
         <v>0.23</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W. NIANG</t>
+          <t>Í. IBAÑEZ SERRANO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3756</v>
+        <v>1.0723</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.4683</v>
+        <v>0.6242</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8439</v>
+        <v>0.4481</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.4177</v>
+        <v>-0.2369</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.8273</v>
+        <v>0.222</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.5904</v>
+        <v>-0.4588</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.7073</v>
+        <v>0.4613</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.721</v>
+        <v>0.4221</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.9864</v>
+        <v>0.0392</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2897</v>
+        <v>-0.6982</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1063</v>
+        <v>-0.2002</v>
       </c>
       <c r="O3" t="n">
-        <v>0.396</v>
+        <v>-0.498</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7308</v>
+        <v>0.2686</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8416</v>
+        <v>0.1629</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8893</v>
+        <v>0.1057</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Í. IBAÑEZ SERRANO</t>
+          <t>W. NIANG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9446</v>
+        <v>0.8361</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7314000000000001</v>
+        <v>-1.8317</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2132</v>
+        <v>2.6677</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2369</v>
+        <v>-3.4177</v>
       </c>
       <c r="H4" t="n">
-        <v>0.222</v>
+        <v>-1.8273</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4588</v>
+        <v>-1.5904</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4613</v>
+        <v>-3.7073</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4221</v>
+        <v>-1.721</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0392</v>
+        <v>-1.9864</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6982</v>
+        <v>0.2897</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2002</v>
+        <v>-0.1063</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.498</v>
+        <v>0.396</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1409</v>
+        <v>1.1913</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2701</v>
+        <v>0.4782</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1292</v>
+        <v>0.7131</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8168</v>
+        <v>0.7249</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4842</v>
+        <v>-0.3118</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3009</v>
+        <v>1.0367</v>
       </c>
       <c r="G5" t="n">
         <v>-1.5872</v>
@@ -844,13 +844,13 @@
         <v>2.0812</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0231</v>
+        <v>1.9313</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5401</v>
+        <v>0.7125</v>
       </c>
       <c r="U5" t="n">
-        <v>1.483</v>
+        <v>1.2188</v>
       </c>
       <c r="V5" t="n">
         <v>3.5026</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5264</v>
+        <v>-1.2072</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0341</v>
+        <v>-1.8617</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5077</v>
+        <v>0.6545</v>
       </c>
       <c r="G6" t="n">
         <v>-2.9814</v>
@@ -922,13 +922,13 @@
         <v>2.4974</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2656</v>
+        <v>1.5848</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3444</v>
+        <v>0.5168</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9212</v>
+        <v>1.068</v>
       </c>
       <c r="V6" t="n">
         <v>0.8137</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2608</v>
+        <v>-1.452</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.164</v>
+        <v>-0.4139</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0968</v>
+        <v>-1.0381</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1448</v>
@@ -1000,13 +1000,13 @@
         <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3647</v>
+        <v>0.4441</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6524</v>
+        <v>0.0977</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2877</v>
+        <v>0.3464</v>
       </c>
       <c r="V7" t="n">
         <v>-1.1675</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4798</v>
+        <v>-1.7591</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0443</v>
+        <v>-0.2942</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4355</v>
+        <v>-1.4649</v>
       </c>
       <c r="G8" t="n">
         <v>0.307</v>
@@ -1078,13 +1078,13 @@
         <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>0.67</v>
+        <v>1.3908</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.109</v>
+        <v>0.6411</v>
       </c>
       <c r="U8" t="n">
-        <v>0.779</v>
+        <v>0.7497</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1675</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5032</v>
+        <v>-3.1957</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.1866</v>
+        <v>-4.5855</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6834</v>
+        <v>1.3898</v>
       </c>
       <c r="G9" t="n">
         <v>0.2608</v>
@@ -1156,13 +1156,13 @@
         <v>1.8731</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2767</v>
+        <v>0.5841</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6524</v>
+        <v>-0.0514</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9291</v>
+        <v>0.6355</v>
       </c>
       <c r="V9" t="n">
         <v>-1.7513</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9385</v>
+        <v>-5.8545</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4198</v>
+        <v>-3.2771</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5187</v>
+        <v>-2.5774</v>
       </c>
       <c r="G10" t="n">
         <v>-3.108</v>
@@ -1234,13 +1234,13 @@
         <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>2.104</v>
+        <v>1.188</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4502</v>
+        <v>0.593</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6538</v>
+        <v>0.595</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6452</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.767900000000001</v>
+        <v>-8.441700000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-12.0666</v>
+        <v>-11.7404</v>
       </c>
       <c r="F11" t="n">
         <v>3.2986</v>
@@ -1288,7 +1288,7 @@
         <v>-0.3248000000000002</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5937000000000001</v>
+        <v>0.5936999999999997</v>
       </c>
       <c r="L11" t="n">
         <v>-0.9185999999999999</v>
@@ -1312,10 +1312,10 @@
         <v>13.5277</v>
       </c>
       <c r="S11" t="n">
-        <v>9.489100000000001</v>
+        <v>9.8154</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6009</v>
+        <v>3.9271</v>
       </c>
       <c r="U11" t="n">
         <v>5.8883</v>
@@ -1324,7 +1324,7 @@
         <v>0.2123000000000004</v>
       </c>
       <c r="W11" t="n">
-        <v>6.509799999999999</v>
+        <v>6.5098</v>
       </c>
       <c r="X11" t="n">
         <v>-6.297600000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.859</v>
+        <v>6.1486</v>
       </c>
       <c r="E12" t="n">
         <v>5.0159</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8431</v>
+        <v>1.1328</v>
       </c>
       <c r="G12" t="n">
         <v>4.1121</v>
@@ -1390,13 +1390,13 @@
         <v>2.4974</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.5878</v>
       </c>
       <c r="T12" t="n">
         <v>-0.6277</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2498</v>
+        <v>0.0398</v>
       </c>
       <c r="V12" t="n">
         <v>1.1675</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7044</v>
+        <v>4.9901</v>
       </c>
       <c r="E13" t="n">
         <v>0.8164</v>
       </c>
       <c r="F13" t="n">
-        <v>3.888</v>
+        <v>4.1737</v>
       </c>
       <c r="G13" t="n">
         <v>3.4152</v>
@@ -1468,13 +1468,13 @@
         <v>2.9137</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5839</v>
+        <v>-0.2981</v>
       </c>
       <c r="T13" t="n">
         <v>-0.6277</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0438</v>
+        <v>0.3295</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>J. BLACK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4876</v>
+        <v>4.7738</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9668</v>
+        <v>1.3598</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5208</v>
+        <v>3.4139</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1934</v>
+        <v>3.247</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4689</v>
+        <v>2.8552</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6624</v>
+        <v>0.3919</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4021</v>
+        <v>3.3085</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6848</v>
+        <v>2.7779</v>
       </c>
       <c r="L14" t="n">
-        <v>3.0869</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2086</v>
+        <v>-0.0615</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7841</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4245</v>
+        <v>-0.1388</v>
       </c>
       <c r="P14" t="n">
-        <v>3.1218</v>
+        <v>0.4162</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2081</v>
+        <v>-3.3299</v>
       </c>
       <c r="R14" t="n">
-        <v>3.3299</v>
+        <v>3.7461</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1814</v>
+        <v>-1.2246</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2271</v>
+        <v>-0.9539</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0457</v>
+        <v>-0.2707</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3538</v>
+        <v>2.3351</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.3351</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. BLACK</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3667</v>
+        <v>3.967</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3598</v>
+        <v>1.5382</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0068</v>
+        <v>2.4288</v>
       </c>
       <c r="G15" t="n">
-        <v>3.247</v>
+        <v>1.1934</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8552</v>
+        <v>-1.4689</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3919</v>
+        <v>2.6624</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3085</v>
+        <v>2.4021</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7779</v>
+        <v>-0.6848</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5306999999999999</v>
+        <v>3.0869</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0615</v>
+        <v>-1.2086</v>
       </c>
       <c r="N15" t="n">
-        <v>0.07729999999999999</v>
+        <v>-0.7841</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1388</v>
+        <v>-0.4245</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4162</v>
+        <v>3.1218</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.3299</v>
+        <v>-0.2081</v>
       </c>
       <c r="R15" t="n">
-        <v>3.7461</v>
+        <v>3.3299</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6317</v>
+        <v>-0.702</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9539</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6778</v>
+        <v>-0.0463</v>
       </c>
       <c r="V15" t="n">
-        <v>2.3351</v>
+        <v>0.3538</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3351</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4779</v>
+        <v>2.5224</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6364</v>
+        <v>1.7436</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8415</v>
+        <v>0.7788</v>
       </c>
       <c r="G16" t="n">
         <v>2.2763</v>
@@ -1702,13 +1702,13 @@
         <v>1.0406</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6309</v>
+        <v>-0.5864</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.64</v>
+        <v>-0.5329</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0092</v>
+        <v>-0.0535</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2969</v>
+        <v>0.4588</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2537</v>
+        <v>-2.1465</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5506</v>
+        <v>2.6054</v>
       </c>
       <c r="G17" t="n">
         <v>2.0797</v>
@@ -1780,13 +1780,13 @@
         <v>1.8731</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8879</v>
+        <v>-0.7259</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4443</v>
+        <v>-0.3372</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4436</v>
+        <v>-0.3888</v>
       </c>
       <c r="V17" t="n">
         <v>0.3538</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0458</v>
+        <v>-0.5966</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4615</v>
+        <v>-0.2472</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5843</v>
+        <v>-0.3494</v>
       </c>
       <c r="G18" t="n">
         <v>0.369</v>
@@ -1858,13 +1858,13 @@
         <v>1.2487</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.496</v>
+        <v>-1.0468</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.2952</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9864000000000001</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>-1.1675</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7416</v>
+        <v>-1.8003</v>
       </c>
       <c r="E19" t="n">
         <v>-2.6116</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8699</v>
+        <v>0.8112</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0248</v>
@@ -1936,13 +1936,13 @@
         <v>1.2487</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1944</v>
+        <v>-0.2531</v>
       </c>
       <c r="T19" t="n">
         <v>-0.3791</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1847</v>
+        <v>0.1259</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6899</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.193</v>
+        <v>-2.8945</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.1145</v>
+        <v>-3.9002</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9215</v>
+        <v>1.0056</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6875</v>
@@ -2014,13 +2014,13 @@
         <v>1.4568</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4431</v>
+        <v>-1.1446</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8358</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6073</v>
+        <v>-0.5232</v>
       </c>
       <c r="V20" t="n">
         <v>-0.23</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.321</v>
+        <v>-2.9829</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.122</v>
+        <v>-2.0149</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.199</v>
+        <v>-0.9681</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1188</v>
@@ -2092,13 +2092,13 @@
         <v>1.0406</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2428</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.48</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.4247</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1231</v>
+        <v>-4.3898</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7608</v>
+        <v>-3.0823</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3623</v>
+        <v>-1.3075</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7171</v>
@@ -2170,13 +2170,13 @@
         <v>1.4568</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3197</v>
+        <v>-0.5864</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0562</v>
+        <v>-0.3776</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2635</v>
+        <v>-0.2087</v>
       </c>
       <c r="V22" t="n">
         <v>-2.3351</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>8.767999999999997</v>
+        <v>10.1966</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.528800000000001</v>
+        <v>-3.5288</v>
       </c>
       <c r="F23" t="n">
-        <v>12.2966</v>
+        <v>13.7252</v>
       </c>
       <c r="G23" t="n">
         <v>10.1445</v>
@@ -2248,13 +2248,13 @@
         <v>21.8524</v>
       </c>
       <c r="S23" t="n">
-        <v>-9.489299999999998</v>
+        <v>-8.0604</v>
       </c>
       <c r="T23" t="n">
-        <v>-5.888599999999999</v>
+        <v>-5.8885</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.6007</v>
+        <v>-2.1722</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2122999999999999</v>
